--- a/processed_ruby_restored_xlsx/sc244_みるく６：花火.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc244_みるく６：花火.ss.xlsx
@@ -788,8 +788,8 @@
       </c>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t>I said it casually, but Miru-chan nodded awkwardly all
-the same.</t>
+          <t>I said it casually, but Miru-chan nodded awkwardly
+all the same.</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -804,8 +804,8 @@
       </c>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t>...Even if I said it on a whim, now that Miru-chan has
-nodded, I can't take it back.</t>
+          <t>...Even if I said it on a whim, now that Miru-chan
+has nodded, I can't take it back.</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -912,8 +912,8 @@
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>Does that mean Miru-chan, at least a little, feels the
-same way I do...？</t>
+          <t>Does that mean Miru-chan, at least a little, feels
+the same way I do...？</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -1459,8 +1459,8 @@
       </c>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>Instead of puffing up to tease me back, Miru-chan asks
-for more herself.</t>
+          <t>Instead of puffing up to tease me back, Miru-chan
+asks for more herself.</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -1748,8 +1748,8 @@
       </c>
       <c r="B85" s="1" t="inlineStr">
         <is>
-          <t>This time we kiss again and again, as if checking each
-other's body heat.</t>
+          <t>This time we kiss again and again, as if checking
+each other's body heat.</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -2281,8 +2281,8 @@
       </c>
       <c r="B120" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan looks back at me and smiles, then dives even
-deeper into our kissing.</t>
+          <t>Miru-chan looks back at me and smiles, then dives
+even deeper into our kissing.</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -2390,8 +2390,8 @@
       </c>
       <c r="B127" s="1" t="inlineStr">
         <is>
-          <t>At that, I could feel Miru-chan’s body starting to get
-flushed.</t>
+          <t>At that, I could feel Miru-chan’s body starting to
+get flushed.</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -2912,8 +2912,8 @@
       </c>
       <c r="B161" s="1" t="inlineStr">
         <is>
-          <t>Thanks to her disheveled yukata, little pink nubs keep
-peeking out from her chest…！</t>
+          <t>Thanks to her disheveled yukata, little pink nubs
+keep peeking out from her chest…！</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -3342,7 +3342,8 @@
       <c r="B189" s="1" t="inlineStr">
         <is>
           <t>She even arches her back and sticks out her breasts
-that still look like they're barely starting to swell.</t>
+that still look like they're barely starting to
+swell.</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -3570,8 +3571,8 @@
       </c>
       <c r="B204" s="1" t="inlineStr">
         <is>
-          <t>Their sensitivity must be off the charts, the pleasure
-concentrated into one point... for sure！</t>
+          <t>Their sensitivity must be off the charts, the
+pleasure concentrated into one point... for sure！</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -4412,8 +4413,8 @@
       </c>
       <c r="B259" s="1" t="inlineStr">
         <is>
-          <t>Hearing that sudden, embarrassed line, I couldn't help
-but smile.</t>
+          <t>Hearing that sudden, embarrassed line, I couldn't
+help but smile.</t>
         </is>
       </c>
       <c r="C259" t="n">
@@ -4658,8 +4659,8 @@
       </c>
       <c r="B275" s="1" t="inlineStr">
         <is>
-          <t>「Hey, if you make a loud noise... everyone might come,
-you know？」</t>
+          <t>「Hey, if you make a loud noise... everyone might
+come, you know？」</t>
         </is>
       </c>
       <c r="C275" t="n">
@@ -4767,8 +4768,8 @@
       </c>
       <c r="B282" s="1" t="inlineStr">
         <is>
-          <t>While checking Miru-chan's nervous reaction, I slid my
-tongue over her chest again.</t>
+          <t>While checking Miru-chan's nervous reaction, I slid
+my tongue over her chest again.</t>
         </is>
       </c>
       <c r="C282" t="n">
@@ -4829,8 +4830,8 @@
       <c r="B286" s="1" t="inlineStr">
         <is>
           <t>The breasts I traced with my tongue felt a different
-softness and firmness than when I touched them with my
-hands.</t>
+softness and firmness than when I touched them with
+my hands.</t>
         </is>
       </c>
       <c r="C286" t="n">
@@ -5062,8 +5063,8 @@
       </c>
       <c r="B301" s="1" t="inlineStr">
         <is>
-          <t>「Chu, geez... chu！ You're starting to taste sweet, you
-know？」</t>
+          <t>「Chu, geez... chu！ You're starting to taste sweet,
+you know？」</t>
         </is>
       </c>
       <c r="C301" t="n">
@@ -5169,8 +5170,8 @@
       </c>
       <c r="B308" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan's words trail off, and she begins to breathe
-out through her nose.</t>
+          <t>Miru-chan's words trail off, and she begins to
+breathe out through her nose.</t>
         </is>
       </c>
       <c r="C308" t="n">
@@ -5185,8 +5186,8 @@
       </c>
       <c r="B309" s="1" t="inlineStr">
         <is>
-          <t>She's probably holding back, trying not to let a sound
-escape and keeping her mouth from opening.</t>
+          <t>She's probably holding back, trying not to let a
+sound escape and keeping her mouth from opening.</t>
         </is>
       </c>
       <c r="C309" t="n">
@@ -5510,8 +5511,8 @@
       </c>
       <c r="B330" s="1" t="inlineStr">
         <is>
-          <t>「My body... heh, nnh！ Boobs... no...！ Nipples... more！
-Moreee...！」</t>
+          <t>「My body... heh, nnh！ Boobs... no...！ Nipples...
+more！ Moreee...！」</t>
         </is>
       </c>
       <c r="C330" t="n">
@@ -6017,8 +6018,8 @@
       </c>
       <c r="B363" s="1" t="inlineStr">
         <is>
-          <t>I carried Miru-chan to a wide chair, held her legs and
-spread them, making her sit.</t>
+          <t>I carried Miru-chan to a wide chair, held her legs
+and spread them, making her sit.</t>
         </is>
       </c>
       <c r="C363" t="n">
@@ -6262,8 +6263,8 @@
       </c>
       <c r="B379" s="1" t="inlineStr">
         <is>
-          <t>By my words, she finally seemed to become aware of her
-position.</t>
+          <t>By my words, she finally seemed to become aware of
+her position.</t>
         </is>
       </c>
       <c r="C379" t="n">
@@ -6616,8 +6617,8 @@
       </c>
       <c r="B402" s="1" t="inlineStr">
         <is>
-          <t>With teasing words that gouged at Miru-chan's shame, I
-looked down at the tight slit.</t>
+          <t>With teasing words that gouged at Miru-chan's shame,
+I looked down at the tight slit.</t>
         </is>
       </c>
       <c r="C402" t="n">
@@ -6906,8 +6907,8 @@
       </c>
       <c r="B421" s="1" t="inlineStr">
         <is>
-          <t>A very pleasurable-sounding moan escaped, and her hips
-gave a faint little thrust upward.</t>
+          <t>A very pleasurable-sounding moan escaped, and her
+hips gave a faint little thrust upward.</t>
         </is>
       </c>
       <c r="C421" t="n">
@@ -7074,8 +7075,9 @@
       </c>
       <c r="B432" s="1" t="inlineStr">
         <is>
-          <t>When I strain my ears, all I can hear is the loud boom
-of the fireworks and everyone's cheerful laughter....</t>
+          <t>When I strain my ears, all I can hear is the loud
+boom of the fireworks and everyone's cheerful
+laughter....</t>
         </is>
       </c>
       <c r="C432" t="n">
@@ -7456,8 +7458,8 @@
       </c>
       <c r="B457" s="1" t="inlineStr">
         <is>
-          <t>As she said herself, I, unable to hold back, thrust my
-hips forward and plunged the penis in all at once.</t>
+          <t>As she said herself, I, unable to hold back, thrust
+my hips forward and plunged the penis in all at once.</t>
         </is>
       </c>
       <c r="C457" t="n">
@@ -7731,8 +7733,8 @@
       </c>
       <c r="B475" s="1" t="inlineStr">
         <is>
-          <t>Her body trembled more than usual, and her hips nearly
-bucked up.</t>
+          <t>Her body trembled more than usual, and her hips
+nearly bucked up.</t>
         </is>
       </c>
       <c r="C475" t="n">
@@ -8395,8 +8397,9 @@
       </c>
       <c r="B518" s="1" t="inlineStr">
         <is>
-          <t>Maybe the angle is off and there's a gap at the joint,
-but a squelching, lewd sound echoes through the car.</t>
+          <t>Maybe the angle is off and there's a gap at the
+joint, but a squelching, lewd sound echoes through
+the car.</t>
         </is>
       </c>
       <c r="C518" t="n">
@@ -8473,8 +8476,9 @@
       </c>
       <c r="B523" s="1" t="inlineStr">
         <is>
-          <t>The love juices leaking from between her legs run down
-Miru-chan's body, tracing her stomach as they drip.</t>
+          <t>The love juices leaking from between her legs run
+down Miru-chan's body, tracing her stomach as they
+drip.</t>
         </is>
       </c>
       <c r="C523" t="n">
@@ -8535,8 +8539,8 @@
       </c>
       <c r="B527" s="1" t="inlineStr">
         <is>
-          <t>「Yeah… your grown-up dick is squelching in Miru-chan’s
-pussy…！」</t>
+          <t>「Yeah… your grown-up dick is squelching in
+Miru-chan’s pussy…！」</t>
         </is>
       </c>
       <c r="C527" t="n">
@@ -8615,8 +8619,8 @@
       </c>
       <c r="B532" s="1" t="inlineStr">
         <is>
-          <t>Already getting worked up all at once, Miru-chan calls
-me at the verge of her climax.</t>
+          <t>Already getting worked up all at once, Miru-chan
+calls me at the verge of her climax.</t>
         </is>
       </c>
       <c r="C532" t="n">
@@ -8862,8 +8866,8 @@
       </c>
       <c r="B548" s="1" t="inlineStr">
         <is>
-          <t>「Fuh-fuaaah！  Ehehe... my pussy, you're swallowing it,
-hehehee」</t>
+          <t>「Fuh-fuaaah！  Ehehe... my pussy, you're swallowing
+it, hehehee」</t>
         </is>
       </c>
       <c r="C548" t="n">
@@ -8924,9 +8928,9 @@
       </c>
       <c r="B552" s="1" t="inlineStr">
         <is>
-          <t>My penis is being squeezed, and if I let my guard down
-even for a second it feels like Miru-chan will take
-everything from me.</t>
+          <t>My penis is being squeezed, and if I let my guard
+down even for a second it feels like Miru-chan will
+take everything from me.</t>
         </is>
       </c>
       <c r="C552" t="n">
@@ -8986,8 +8990,8 @@
       </c>
       <c r="B556" s="1" t="inlineStr">
         <is>
-          <t>「Ha ha... so many such good sounds... fuu, I'm getting
-excited... ahh！」</t>
+          <t>「Ha ha... so many such good sounds... fuu, I'm
+getting excited... ahh！」</t>
         </is>
       </c>
       <c r="C556" t="n">
@@ -9125,8 +9129,9 @@
       </c>
       <c r="B565" s="1" t="inlineStr">
         <is>
-          <t>If the bus could carry us into a world of just the two
-of us, I even started thinking such strange things.</t>
+          <t>If the bus could carry us into a world of just the
+two of us, I even started thinking such strange
+things.</t>
         </is>
       </c>
       <c r="C565" t="n">
@@ -9217,8 +9222,8 @@
       </c>
       <c r="B571" s="1" t="inlineStr">
         <is>
-          <t>It was as if she were telling me to come together with
-her.</t>
+          <t>It was as if she were telling me to come together
+with her.</t>
         </is>
       </c>
       <c r="C571" t="n">
@@ -9293,8 +9298,8 @@
       </c>
       <c r="B576" s="1" t="inlineStr">
         <is>
-          <t>What I could hear was the loud boom of fireworks going
-off.</t>
+          <t>What I could hear was the loud boom of fireworks
+going off.</t>
         </is>
       </c>
       <c r="C576" t="n">
@@ -9356,8 +9361,8 @@
       </c>
       <c r="B580" s="1" t="inlineStr">
         <is>
-          <t>「Miru！ Ah！ It's going crazy... nhah！ I'm gonna... ahh！
-Uuu！」</t>
+          <t>「Miru！ Ah！ It's going crazy... nhah！ I'm gonna...
+ahh！ Uuu！」</t>
         </is>
       </c>
       <c r="C580" t="n">
@@ -9559,7 +9564,8 @@
       <c r="B593" s="1" t="inlineStr">
         <is>
           <t>Now, matching the fireworks and the tremors of our
-bodies, my hips move on their own and start thrashing.</t>
+bodies, my hips move on their own and start
+thrashing.</t>
         </is>
       </c>
       <c r="C593" t="n">
@@ -9574,8 +9580,8 @@
       </c>
       <c r="B594" s="1" t="inlineStr">
         <is>
-          <t>Seeking nothing but pure pleasure, we desperately call
-each other's names.</t>
+          <t>Seeking nothing but pure pleasure, we desperately
+call each other's names.</t>
         </is>
       </c>
       <c r="C594" t="n">
@@ -10739,8 +10745,8 @@
       <c r="B670" s="1" t="inlineStr">
         <is>
           <t>The instant the light flashed, Miru-chan’s
-between-her-legs, slick with semen, was seared onto my
-retina…！</t>
+between-her-legs, slick with semen, was seared onto
+my retina…！</t>
         </is>
       </c>
       <c r="C670" t="n">
@@ -10878,8 +10884,8 @@
       <c r="B679" s="1" t="inlineStr">
         <is>
           <t>Moreover, the semen, gushing out with increasing
-force, lands mercilessly not only between her legs but
-even splatters onto her yukata...</t>
+force, lands mercilessly not only between her legs
+but even splatters onto her yukata...</t>
         </is>
       </c>
       <c r="C679" t="n">
@@ -11260,9 +11266,9 @@
       </c>
       <c r="B704" s="1" t="inlineStr">
         <is>
-          <t>Worried by Miru-chan's fading, barely audible voice, I
-managed to lift my body somehow using the strength in
-my arms.</t>
+          <t>Worried by Miru-chan's fading, barely audible voice,
+I managed to lift my body somehow using the strength
+in my arms.</t>
         </is>
       </c>
       <c r="C704" t="n">
@@ -11565,8 +11571,8 @@
       </c>
       <c r="B724" s="1" t="inlineStr">
         <is>
-          <t>At the moment the fireworks' light suddenly lit up her
-face, her embarrassed expression became clearly
+          <t>At the moment the fireworks' light suddenly lit up
+her face, her embarrassed expression became clearly
 visible.</t>
         </is>
       </c>

--- a/processed_ruby_restored_xlsx/sc244_みるく６：花火.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc244_みるく６：花火.ss.xlsx
@@ -913,7 +913,7 @@
       <c r="B30" s="1" t="inlineStr">
         <is>
           <t>Does that mean Miru-chan, at least a little, feels
-the same way I do...？</t>
+the same way I do...？"</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -3633,7 +3633,7 @@
       </c>
       <c r="B208" s="1" t="inlineStr">
         <is>
-          <t>「Nnngh... nn！  Mmm...」</t>
+          <t>Nnngh... nn！  Mmm...</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -3679,8 +3679,8 @@
       </c>
       <c r="B211" s="1" t="inlineStr">
         <is>
-          <t>「Ah, if you keep looking like that... it's
-embarrassing」</t>
+          <t>Ah, if you keep looking like that... it's
+embarrassing</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="B213" s="1" t="inlineStr">
         <is>
-          <t>「Nnff...！　Miru-chaaan！」</t>
+          <t>Nnff...！　Miru-chaaan！</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="B215" s="1" t="inlineStr">
         <is>
-          <t>「Fuwa！？　Fuwawawawa！」</t>
+          <t>Fuwa！？　Fuwawawawa！</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="B219" s="1" t="inlineStr">
         <is>
-          <t>「Uwa, ah！ Wh-what are you doing...！」</t>
+          <t>Uwa, ah！ Wh-what are you doing...！</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="B230" s="1" t="inlineStr">
         <is>
-          <t>Dragging my tongue theatrically across her breast,
+          <t>Dragging his tongue theatrically across her breast,
 Miru lets out a high, clear cry.</t>
         </is>
       </c>
@@ -4015,8 +4015,8 @@
       </c>
       <c r="B233" s="1" t="inlineStr">
         <is>
-          <t>Sluurrrp...！  I make the sound on purpose as I suck
-and lap with my tongue.</t>
+          <t>Sluurrrp...！  He makes the sound on purpose as he
+sucks and laps with his tongue.</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="B237" s="1" t="inlineStr">
         <is>
-          <t>When I pull away, Miru has this dazed look on her
+          <t>When he pulls away, Miru has this dazed look on her
 face.</t>
         </is>
       </c>
@@ -5001,8 +5001,8 @@
       </c>
       <c r="B297" s="1" t="inlineStr">
         <is>
-          <t>「Nngh, fuh... ha！ My body... ah！ It's getting hot,
-slowly... cut—uu...」</t>
+          <t>Nngh, fuh... ha！ My body... ah！ It's getting hot,
+slowly... cut—uu...</t>
         </is>
       </c>
       <c r="C297" t="n">
@@ -5094,7 +5094,7 @@
       </c>
       <c r="B303" s="1" t="inlineStr">
         <is>
-          <t>「Mi- Miru doesn't have boobs, y'know」</t>
+          <t>Mi- Miru doesn't have boobs, y'know</t>
         </is>
       </c>
       <c r="C303" t="n">
@@ -5186,8 +5186,8 @@
       </c>
       <c r="B309" s="1" t="inlineStr">
         <is>
-          <t>She's probably holding back, trying not to let a
-sound escape and keeping her mouth from opening.</t>
+          <t>They're probably holding back, trying not to let a
+sound escape and keeping their mouth from opening.</t>
         </is>
       </c>
       <c r="C309" t="n">
@@ -6356,7 +6356,7 @@
       </c>
       <c r="B385" s="1" t="inlineStr">
         <is>
-          <t>「Awa—… Yaan！」</t>
+          <t>Awa—… Yaan！</t>
         </is>
       </c>
       <c r="C385" t="n">
@@ -6387,7 +6387,7 @@
       </c>
       <c r="B387" s="1" t="inlineStr">
         <is>
-          <t>But because I'm holding her ankle, her body sways
+          <t>But because I'm holding their ankle, their body sways
 gently.</t>
         </is>
       </c>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="B389" s="1" t="inlineStr">
         <is>
-          <t>「I knew it... Onii-chan, you're such a pervert...」</t>
+          <t>I knew it... Onii-chan, you're such a pervert...</t>
         </is>
       </c>
       <c r="C389" t="n">
@@ -6618,7 +6618,7 @@
       <c r="B402" s="1" t="inlineStr">
         <is>
           <t>With teasing words that gouged at Miru-chan's shame,
-I looked down at the tight slit.</t>
+he looked down at the tight slit."</t>
         </is>
       </c>
       <c r="C402" t="n">
@@ -6634,7 +6634,7 @@
       <c r="B403" s="1" t="inlineStr">
         <is>
           <t>Indeed, it was wet enough that you could tell just by
-looking.</t>
+looking."</t>
         </is>
       </c>
       <c r="C403" t="n">
@@ -7183,8 +7183,8 @@
       </c>
       <c r="B439" s="1" t="inlineStr">
         <is>
-          <t>「Nn, nnfuu...？ I-Isn't it... gotten bigger than
-before？」</t>
+          <t>Nn, nnfuu...？ I-Isn't it... gotten bigger than
+before？</t>
         </is>
       </c>
       <c r="C439" t="n">
@@ -7535,7 +7535,7 @@
       </c>
       <c r="B462" s="1" t="inlineStr">
         <is>
-          <t>And if I just pushed my penis all the way in like
+          <t>And if he just pushed his penis all the way in like
 that...</t>
         </is>
       </c>
@@ -7641,7 +7641,7 @@
       </c>
       <c r="B469" s="1" t="inlineStr">
         <is>
-          <t>「This is… nngh！ It's totally wrong！」</t>
+          <t>This is… nngh！ It's totally wrong！</t>
         </is>
       </c>
       <c r="C469" t="n">
@@ -7859,7 +7859,7 @@
         <is>
           <t>Maybe she feels satisfied thinking about sharing this
 space with just the two of us, more than worrying
-about everyone else...？</t>
+about everyone else...？"</t>
         </is>
       </c>
       <c r="C483" t="n">
@@ -7922,7 +7922,7 @@
         <is>
           <t>Partly it looks painful, but her face is completely
 blissed out, and both her heart and body are
-fulfilled...</t>
+fulfilled..."</t>
         </is>
       </c>
       <c r="C487" t="n">
@@ -8029,7 +8029,7 @@
       <c r="B494" s="1" t="inlineStr">
         <is>
           <t>I bend my legs and drive my whole body into conveying
-everything I feel to Miru-chan...！</t>
+everything I feel to Miru-chan...！"</t>
         </is>
       </c>
       <c r="C494" t="n">
@@ -8306,7 +8306,7 @@
       </c>
       <c r="B512" s="1" t="inlineStr">
         <is>
-          <t>「Fwaaah... my body's gonna melt...」</t>
+          <t>Fwaaah... my body's gonna melt...</t>
         </is>
       </c>
       <c r="C512" t="n">
@@ -8336,7 +8336,7 @@
       </c>
       <c r="B514" s="1" t="inlineStr">
         <is>
-          <t>「Yeah... me too...！！」</t>
+          <t>Yeah... me too...！！</t>
         </is>
       </c>
       <c r="C514" t="n">
@@ -8366,7 +8366,7 @@
       </c>
       <c r="B516" s="1" t="inlineStr">
         <is>
-          <t>「Ah, haa... nng！ Uuuh, hah！ Haa！」</t>
+          <t>Ah, haa... nng！ Uuuh, hah！ Haa！</t>
         </is>
       </c>
       <c r="C516" t="n">
@@ -8666,8 +8666,8 @@
       </c>
       <c r="B535" s="1" t="inlineStr">
         <is>
-          <t>Answering Miru-chan’s words, I keep stimulating her
-with my penis...！</t>
+          <t>Answering Miru-chan's words, I keep stimulating her
+penis...！"</t>
         </is>
       </c>
       <c r="C535" t="n">
@@ -8960,7 +8960,7 @@
       </c>
       <c r="B554" s="1" t="inlineStr">
         <is>
-          <t>「Fah, aaah... Hah！ Haa, nmm！」</t>
+          <t>Fah, aaah... Hah！ Haa, nmm！</t>
         </is>
       </c>
       <c r="C554" t="n">
@@ -9516,9 +9516,9 @@
       </c>
       <c r="B590" s="1" t="inlineStr">
         <is>
-          <t>The rubbing sound of my penis against my vaginal wall
-grows stronger and stronger, and my excitement builds
-up！</t>
+          <t>The rubbing sound of his penis against my vaginal
+wall grows stronger and stronger, and my excitement
+builds up！</t>
         </is>
       </c>
       <c r="C590" t="n">
@@ -9885,7 +9885,7 @@
       </c>
       <c r="B614" s="1" t="inlineStr">
         <is>
-          <t>「Nnnn~~！ Ah, ah！ Aah, ah！ Haaah...！」</t>
+          <t>Nnnn~~！ Ah, ah！ Aah, ah！ Haaah...！</t>
         </is>
       </c>
       <c r="C614" t="n">
@@ -9915,8 +9915,8 @@
       </c>
       <c r="B616" s="1" t="inlineStr">
         <is>
-          <t>「Nnnhh aaah, it's coming out... ahah! I'm cumming...
-uaaah」</t>
+          <t>Nnnhh aaah, it's coming out... ahah! I'm cumming...
+uaaah</t>
         </is>
       </c>
       <c r="C616" t="n">
@@ -9946,7 +9946,8 @@
       </c>
       <c r="B618" s="1" t="inlineStr">
         <is>
-          <t>And my penis trembled and then released a huge lump…！</t>
+          <t>And his penis trembled and then released a huge
+lump…！</t>
         </is>
       </c>
       <c r="C618" t="n">
@@ -10177,7 +10178,7 @@
       </c>
       <c r="B633" s="1" t="inlineStr">
         <is>
-          <t>「Ahh! I-it's c-coming… being squeezed out, hah!」</t>
+          <t>Ahh! I-it's c-coming… being squeezed out, hah!</t>
         </is>
       </c>
       <c r="C633" t="n">
@@ -10298,7 +10299,7 @@
       </c>
       <c r="B641" s="1" t="inlineStr">
         <is>
-          <t>「Ugh, haa…！」</t>
+          <t>Ugh, haa…！</t>
         </is>
       </c>
       <c r="C641" t="n">
@@ -10343,7 +10344,7 @@
       </c>
       <c r="B644" s="1" t="inlineStr">
         <is>
-          <t>「Kyaa！」</t>
+          <t>Kyaa！</t>
         </is>
       </c>
       <c r="C644" t="n">
@@ -10634,7 +10635,7 @@
       </c>
       <c r="B663" s="1" t="inlineStr">
         <is>
-          <t>Because my penis was pulsing and thrashing, it shot
+          <t>Because his penis was pulsing and thrashing, it shot
 out...！</t>
         </is>
       </c>
@@ -10650,7 +10651,7 @@
       </c>
       <c r="B664" s="1" t="inlineStr">
         <is>
-          <t>At the same time my ejaculation began, and the semen
+          <t>At the same time his ejaculation began, and the semen
 arcing high through the air fell onto Miru-chan's
 between-her-legs….</t>
         </is>
@@ -10867,7 +10868,7 @@
       </c>
       <c r="B678" s="1" t="inlineStr">
         <is>
-          <t>Having witnessed the arousing sight, my penis keeps
+          <t>Having witnessed the arousing sight, his penis keeps
 ejaculating more.</t>
         </is>
       </c>
@@ -10915,7 +10916,7 @@
       </c>
       <c r="B681" s="1" t="inlineStr">
         <is>
-          <t>「Uhh…！ Uhh… fuu…！ Ah, aa… oniichan…n！ Muuu…！？」</t>
+          <t>Uhh…！ Uhh… fuu…！ Ah, aa… oniichan…n！ Muuu…！？</t>
         </is>
       </c>
       <c r="C681" t="n">
@@ -10990,7 +10991,7 @@
       </c>
       <c r="B686" s="1" t="inlineStr">
         <is>
-          <t>「Nnffuu！　Fuu！　Fuuu…！」</t>
+          <t>Nnffuu！　Fuu！　Fuuu…！</t>
         </is>
       </c>
       <c r="C686" t="n">
@@ -11082,7 +11083,7 @@
       </c>
       <c r="B692" s="1" t="inlineStr">
         <is>
-          <t>I, entranced, held her butt and stared at it
+          <t>I, entranced, held their butt and stared at it
 intently….</t>
         </is>
       </c>
@@ -11314,7 +11315,7 @@
       </c>
       <c r="B707" s="1" t="inlineStr">
         <is>
-          <t>「My waist... won't move...」</t>
+          <t>My waist... won't move...</t>
         </is>
       </c>
       <c r="C707" t="n">
@@ -11618,7 +11619,7 @@
       </c>
       <c r="B727" s="1" t="inlineStr">
         <is>
-          <t>My heart racing, I muttered without thinking, and
+          <t>His heart racing, he muttered without thinking, and
 Miru-chan flushed even more.</t>
         </is>
       </c>
